--- a/uda/attachments/object-access/RITM123456.xlsx
+++ b/uda/attachments/object-access/RITM123456.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228" codeName="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228" codeName="{26A90621-87C4-6C01-FD6A-EE6E7C140903}"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fumajeed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D606D96E-41FA-4172-8DD4-4213F43E5D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9EC823-7750-439C-88B2-C1BB04199554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E24ABC1B-7E95-4B18-A5F6-77291EA68DD2}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Approval_Req" sheetId="4" r:id="rId3"/>
     <sheet name="Reference" sheetId="5" state="hidden" r:id="rId4"/>
   </sheets>
+  <functionGroups builtInGroupCount="19"/>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Approval_Req!$A$1:$K$633</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reference!$A$1:$A$37</definedName>
@@ -3616,15 +3617,9 @@
     <t>Prod</t>
   </si>
   <si>
-    <t>furqan54@legacy.com</t>
-  </si>
-  <si>
     <t>Need for cpo</t>
   </si>
   <si>
-    <t>Add object</t>
-  </si>
-  <si>
     <t>Azure</t>
   </si>
   <si>
@@ -3638,6 +3633,12 @@
   </si>
   <si>
     <t>Permanent</t>
+  </si>
+  <si>
+    <t>furqan@54egacy.com</t>
+  </si>
+  <si>
+    <t>Remove object</t>
   </si>
 </sst>
 </file>
@@ -5206,6 +5207,16 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5219,16 +5230,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -5605,7 +5606,7 @@
       <c r="B6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="182">
+      <c r="C6" s="178">
         <v>46258</v>
       </c>
       <c r="D6" s="53"/>
@@ -5681,8 +5682,8 @@
       <c r="B12" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="183" t="s">
-        <v>1130</v>
+      <c r="C12" s="179" t="s">
+        <v>1136</v>
       </c>
       <c r="D12" s="57" t="s">
         <v>22</v>
@@ -5717,10 +5718,10 @@
       <c r="B15" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="180" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D15" s="181"/>
+      <c r="C15" s="183" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D15" s="184"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="33" t="s">
@@ -5731,12 +5732,12 @@
       <c r="D16" s="36"/>
     </row>
     <row r="17" spans="1:4" ht="20.5" customHeight="1">
-      <c r="A17" s="179" t="s">
+      <c r="A17" s="182" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="179"/>
-      <c r="C17" s="179"/>
-      <c r="D17" s="179"/>
+      <c r="B17" s="182"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
     </row>
     <row r="18" spans="1:4" ht="26">
       <c r="A18" s="23" t="s">
@@ -5755,18 +5756,18 @@
       <c r="B19" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="184">
+      <c r="C19" s="180">
         <v>46258</v>
       </c>
       <c r="D19" s="17"/>
     </row>
     <row r="20" spans="1:4" ht="20.5" customHeight="1">
-      <c r="A20" s="178" t="s">
+      <c r="A20" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="178"/>
-      <c r="C20" s="178"/>
-      <c r="D20" s="178"/>
+      <c r="B20" s="181"/>
+      <c r="C20" s="181"/>
+      <c r="D20" s="181"/>
     </row>
     <row r="21" spans="1:4" ht="97" customHeight="1">
       <c r="A21" s="19" t="s">
@@ -5895,25 +5896,25 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="108" t="s">
         <v>1132</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="H3" s="102" t="s">
         <v>1133</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="108" t="s">
+      <c r="I3" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>1134</v>
-      </c>
-      <c r="H3" s="102" t="s">
-        <v>1135</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>1137</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -12660,7 +12661,7 @@
     </row>
     <row r="200" spans="1:11" ht="14.5">
       <c r="A200" s="107" t="str">
-        <f t="shared" ref="A200:A231" si="6">UPPER(CONCATENATE(TRIM(B200),".",TRIM(C200)))</f>
+        <f t="shared" ref="A200:A208" si="6">UPPER(CONCATENATE(TRIM(B200),".",TRIM(C200)))</f>
         <v>VW_RAWSTD__ONEVIZION.</v>
       </c>
       <c r="B200" s="4" t="s">
@@ -19394,7 +19395,7 @@
     </row>
     <row r="402" spans="1:11">
       <c r="A402" s="152" t="str">
-        <f t="shared" ref="A402:A465" si="10">UPPER(CONCATENATE(TRIM(B402),".",TRIM(C402)))</f>
+        <f t="shared" ref="A402:A450" si="10">UPPER(CONCATENATE(TRIM(B402),".",TRIM(C402)))</f>
         <v>VW_RAWSTD__ELA_HRHUB.</v>
       </c>
       <c r="B402" s="88" t="s">
@@ -22181,7 +22182,7 @@
     </row>
     <row r="485" spans="1:11">
       <c r="A485" s="87" t="str">
-        <f t="shared" ref="A485:A516" si="13">UPPER(CONCATENATE(TRIM(B485),".",TRIM(C485)))</f>
+        <f t="shared" ref="A485:A505" si="13">UPPER(CONCATENATE(TRIM(B485),".",TRIM(C485)))</f>
         <v>VW_DRVD__APP_CUSTOMER_JOURNEY.</v>
       </c>
       <c r="B485" s="4" t="s">
@@ -27733,6 +27734,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
+    <TaxCatchAll xmlns="038c8c0e-8094-4ce0-bcc3-443d0227a358" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="038c8c0e-8094-4ce0-bcc3-443d0227a358">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e486f8b4-eebb-4608-84e1-7dfc34584798">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F8D78C1B0C4B3C4484BB76465D1BD4FA" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a1f1aa0efb497eae2d32dacfe35760b9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="http://schemas.microsoft.com/sharepoint/v4" xmlns:ns3="038c8c0e-8094-4ce0-bcc3-443d0227a358" xmlns:ns4="e486f8b4-eebb-4608-84e1-7dfc34584798" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="69efe8c2d08b5190508b8c39e6f532b0" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v4"/>
@@ -27980,31 +28005,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37CC5514-14FF-4154-BC1C-E7D870D3B17D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="038c8c0e-8094-4ce0-bcc3-443d0227a358"/>
+    <ds:schemaRef ds:uri="e486f8b4-eebb-4608-84e1-7dfc34584798"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
-    <TaxCatchAll xmlns="038c8c0e-8094-4ce0-bcc3-443d0227a358" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="038c8c0e-8094-4ce0-bcc3-443d0227a358">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e486f8b4-eebb-4608-84e1-7dfc34584798">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BCD9D9D-1246-44D7-BEF2-FEA0DD9BEFE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57933513-9678-41C8-BA53-067BA12884D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28024,26 +28045,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BCD9D9D-1246-44D7-BEF2-FEA0DD9BEFE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37CC5514-14FF-4154-BC1C-E7D870D3B17D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
-    <ds:schemaRef ds:uri="038c8c0e-8094-4ce0-bcc3-443d0227a358"/>
-    <ds:schemaRef ds:uri="e486f8b4-eebb-4608-84e1-7dfc34584798"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e760c494-6550-44b4-8258-77c175d778b7}" enabled="1" method="Privileged" siteId="{76a2ae5a-9f00-4f6b-95ed-5d33d77c4d61}" contentBits="0" removed="0"/>

--- a/uda/attachments/object-access/RITM123456.xlsx
+++ b/uda/attachments/object-access/RITM123456.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fumajeed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9EC823-7750-439C-88B2-C1BB04199554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02955D4-7200-4458-8E47-6FD4C259EE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E24ABC1B-7E95-4B18-A5F6-77291EA68DD2}"/>
+    <workbookView xWindow="1780" yWindow="1780" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{E24ABC1B-7E95-4B18-A5F6-77291EA68DD2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Request Info" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Approval_Req" sheetId="4" r:id="rId3"/>
     <sheet name="Reference" sheetId="5" state="hidden" r:id="rId4"/>
   </sheets>
-  <functionGroups builtInGroupCount="19"/>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Approval_Req!$A$1:$K$633</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reference!$A$1:$A$37</definedName>
@@ -3638,7 +3637,7 @@
     <t>furqan@54egacy.com</t>
   </si>
   <si>
-    <t>Remove object</t>
+    <t>Add object</t>
   </si>
 </sst>
 </file>
@@ -27734,30 +27733,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
-    <TaxCatchAll xmlns="038c8c0e-8094-4ce0-bcc3-443d0227a358" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="038c8c0e-8094-4ce0-bcc3-443d0227a358">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e486f8b4-eebb-4608-84e1-7dfc34584798">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F8D78C1B0C4B3C4484BB76465D1BD4FA" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a1f1aa0efb497eae2d32dacfe35760b9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="http://schemas.microsoft.com/sharepoint/v4" xmlns:ns3="038c8c0e-8094-4ce0-bcc3-443d0227a358" xmlns:ns4="e486f8b4-eebb-4608-84e1-7dfc34584798" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="69efe8c2d08b5190508b8c39e6f532b0" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v4"/>
@@ -28005,27 +27980,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37CC5514-14FF-4154-BC1C-E7D870D3B17D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
-    <ds:schemaRef ds:uri="038c8c0e-8094-4ce0-bcc3-443d0227a358"/>
-    <ds:schemaRef ds:uri="e486f8b4-eebb-4608-84e1-7dfc34584798"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BCD9D9D-1246-44D7-BEF2-FEA0DD9BEFE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
+    <TaxCatchAll xmlns="038c8c0e-8094-4ce0-bcc3-443d0227a358" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="038c8c0e-8094-4ce0-bcc3-443d0227a358">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e486f8b4-eebb-4608-84e1-7dfc34584798">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57933513-9678-41C8-BA53-067BA12884D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28045,6 +28024,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BCD9D9D-1246-44D7-BEF2-FEA0DD9BEFE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37CC5514-14FF-4154-BC1C-E7D870D3B17D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="038c8c0e-8094-4ce0-bcc3-443d0227a358"/>
+    <ds:schemaRef ds:uri="e486f8b4-eebb-4608-84e1-7dfc34584798"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e760c494-6550-44b4-8258-77c175d778b7}" enabled="1" method="Privileged" siteId="{76a2ae5a-9f00-4f6b-95ed-5d33d77c4d61}" contentBits="0" removed="0"/>
